--- a/data/trans_orig/P80_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P80_2023-Provincia-trans_orig.xlsx
@@ -725,27 +725,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>311274</t>
+          <t>317983</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>310592</t>
+          <t>314020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>288069</t>
+          <t>314973</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>280756</t>
+          <t>310688</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>599342</t>
+          <t>632957</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>591730</t>
+          <t>628624</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>862</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1187,12 +1187,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>6282</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>511409</t>
+          <t>524318</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>491811</t>
+          <t>512485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>516879</t>
+          <t>529271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>507414</t>
+          <t>539089</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>501057</t>
+          <t>533093</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>510881</t>
+          <t>542617</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1018822</t>
+          <t>1063406</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1003122</t>
+          <t>1049616</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1025778</t>
+          <t>1069744</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23362</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>5972</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21284</t>
+          <t>18599</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>703</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3642</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1369</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2087</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>7283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>3457</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>879</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10424</t>
+          <t>9397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>513656</t>
+          <t>545175</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>513656</t>
+          <t>545175</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>513656</t>
+          <t>545175</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1032045</t>
+          <t>1075822</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1032045</t>
+          <t>1075822</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1032045</t>
+          <t>1075822</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>309108</t>
+          <t>306078</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>302924</t>
+          <t>297163</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>312830</t>
+          <t>310751</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>341452</t>
+          <t>348816</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>334977</t>
+          <t>342741</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>345275</t>
+          <t>352944</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>650559</t>
+          <t>654895</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>642436</t>
+          <t>645267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>656333</t>
+          <t>661614</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8634</t>
+          <t>8675</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>9468</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16998</t>
+          <t>16390</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2343</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>612</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>5463</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1745</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1594</t>
+          <t>1507</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>7356</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>309040</t>
+          <t>369529</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>302097</t>
+          <t>359738</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>311836</t>
+          <t>372064</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>471525</t>
+          <t>417574</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>463236</t>
+          <t>410785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>474372</t>
+          <t>420530</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>780564</t>
+          <t>787104</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>772725</t>
+          <t>778407</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>785165</t>
+          <t>791858</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2929,12 +2929,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4373</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,22 +2954,22 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2386</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>567</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>7048</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3007,12 +3007,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>11265</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4797</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>10779</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8419</t>
+          <t>7506</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>9662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -3488,27 +3488,27 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>205040</t>
+          <t>222995</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>200722</t>
+          <t>218243</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>383106</t>
+          <t>427925</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>378885</t>
+          <t>421758</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>384589</t>
+          <t>429621</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5704</t>
+          <t>7863</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>178066</t>
+          <t>204930</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>206523</t>
+          <t>224691</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>384589</t>
+          <t>429621</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>384589</t>
+          <t>429621</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>384589</t>
+          <t>429621</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>266515</t>
+          <t>267751</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>262250</t>
+          <t>263854</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>268777</t>
+          <t>269904</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>255941</t>
+          <t>262191</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>253447</t>
+          <t>259496</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>256896</t>
+          <t>263391</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>522456</t>
+          <t>529942</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>517867</t>
+          <t>525225</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>525148</t>
+          <t>532534</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6460</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>591</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3093</t>
+          <t>3358</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>3220</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>818</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>7612</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>968</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>968</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>502</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>502</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
@@ -4667,12 +4667,12 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>602021</t>
+          <t>691829</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>585148</t>
+          <t>672757</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>611721</t>
+          <t>703858</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,67 +4852,67 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>831094</t>
+          <t>750441</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>820582</t>
+          <t>739326</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>840778</t>
+          <t>757497</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>98,51%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>1517</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>1442270</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>1422846</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>1456754</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
           <t>96,95%</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>99,33%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>1517</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>1433114</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>1413279</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>1447814</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>10735</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>3934</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>20003</t>
+          <t>24995</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>13703</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>6042</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>27930</t>
+          <t>30561</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>9821</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>3675</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>18568</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>768</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>23353</t>
+          <t>27864</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4076</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>13075</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3448</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5269,7 +5269,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>2238</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>6030</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,12 +5339,12 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>9881</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
@@ -5354,17 +5354,17 @@
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>623349</t>
+          <t>718698</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>623349</t>
+          <t>718698</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>623349</t>
+          <t>718698</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>846418</t>
+          <t>768951</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>846418</t>
+          <t>768951</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>846418</t>
+          <t>768951</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1469766</t>
+          <t>1487649</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1469766</t>
+          <t>1487649</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1469766</t>
+          <t>1487649</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>904358</t>
+          <t>768428</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>890127</t>
+          <t>756253</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>918115</t>
+          <t>778355</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5534,67 +5534,67 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>704938</t>
+          <t>815725</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>697611</t>
+          <t>806965</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>710501</t>
+          <t>821736</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>1584154</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>1567941</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>1596045</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
           <t>97,37%</t>
         </is>
       </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>1781</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>1609296</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>1594636</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>1623887</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -5612,32 +5612,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>18606</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>11298</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>29356</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5647,27 +5647,27 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>4809</t>
+          <t>5460</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1755</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>24065</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>15281</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>32550</t>
+          <t>35758</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5725,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>7014</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>18559</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5760,32 +5760,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>12786</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>11615</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>20956</t>
+          <t>25473</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>752</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -5848,12 +5848,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>4374</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4817</t>
+          <t>4441</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>678</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3613</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,3%</t>
         </is>
       </c>
     </row>
@@ -6064,17 +6064,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>927714</t>
+          <t>796952</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>927714</t>
+          <t>796952</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>927714</t>
+          <t>796952</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6099,17 +6099,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>716487</t>
+          <t>829960</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>716487</t>
+          <t>829960</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>716487</t>
+          <t>829960</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>1644201</t>
+          <t>1626913</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>1644201</t>
+          <t>1626913</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>1644201</t>
+          <t>1626913</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6181,32 +6181,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>3391790</t>
+          <t>3450847</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>3368649</t>
+          <t>3424953</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>3412246</t>
+          <t>3469150</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6216,32 +6216,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>3605471</t>
+          <t>3671806</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>3591344</t>
+          <t>3656141</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3618615</t>
+          <t>3683414</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>6997261</t>
+          <t>7122653</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>6970720</t>
+          <t>7092094</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>7020570</t>
+          <t>7146288</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,48%</t>
         </is>
       </c>
     </row>
@@ -6294,32 +6294,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>37190</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>28895</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>57305</t>
+          <t>63289</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6329,32 +6329,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>18810</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>54053</t>
+          <t>61038</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>39076</t>
+          <t>46894</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>73596</t>
+          <t>80997</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -6407,32 +6407,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>17455</t>
+          <t>23478</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>13621</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>29751</t>
+          <t>38891</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6442,32 +6442,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>14411</t>
+          <t>16391</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>10509</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>23671</t>
+          <t>27125</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>31866</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>20751</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>47070</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -6520,32 +6520,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>15941</t>
+          <t>19714</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6555,17 +6555,17 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1532</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>10711</t>
+          <t>10922</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4086</t>
+          <t>6642</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>20261</t>
+          <t>24670</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4971</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1850</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>11436</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6668,32 +6668,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>13614</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>24471</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>17983</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>28699</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -6746,17 +6746,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>3457204</t>
+          <t>3529919</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6781,17 +6781,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3654619</t>
+          <t>3726931</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>7111823</t>
+          <t>7256850</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
